--- a/ig/175-upgrade-app-profiles/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/175-upgrade-app-profiles/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-14T10:16:17+00:00</t>
+    <t>2024-02-14T11:10:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -6041,7 +6041,7 @@
         <v>74</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>82</v>
@@ -15691,7 +15691,7 @@
         <v>74</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>82</v>
@@ -15795,7 +15795,7 @@
         <v>74</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>73</v>
@@ -16101,7 +16101,7 @@
         <v>74</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>73</v>
@@ -16205,7 +16205,7 @@
         <v>74</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>73</v>
@@ -16309,7 +16309,7 @@
         <v>74</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>82</v>
@@ -16411,7 +16411,7 @@
         <v>74</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>82</v>
@@ -16615,7 +16615,7 @@
         <v>74</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>82</v>
@@ -16717,7 +16717,7 @@
         <v>74</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>73</v>
@@ -18663,7 +18663,7 @@
         <v>74</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>73</v>
@@ -18869,7 +18869,7 @@
         <v>74</v>
       </c>
       <c r="G145" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H145" t="s" s="2">
         <v>73</v>
@@ -19377,7 +19377,7 @@
         <v>74</v>
       </c>
       <c r="G150" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H150" t="s" s="2">
         <v>73</v>
@@ -31525,7 +31525,7 @@
         <v>74</v>
       </c>
       <c r="G268" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H268" t="s" s="2">
         <v>73</v>
@@ -31629,7 +31629,7 @@
         <v>74</v>
       </c>
       <c r="G269" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H269" t="s" s="2">
         <v>73</v>
@@ -32241,7 +32241,7 @@
         <v>74</v>
       </c>
       <c r="G275" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H275" t="s" s="2">
         <v>73</v>
@@ -45619,7 +45619,7 @@
         <v>74</v>
       </c>
       <c r="G405" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H405" t="s" s="2">
         <v>73</v>
@@ -58487,7 +58487,7 @@
         <v>74</v>
       </c>
       <c r="G530" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H530" t="s" s="2">
         <v>73</v>
@@ -58997,7 +58997,7 @@
         <v>74</v>
       </c>
       <c r="G535" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H535" t="s" s="2">
         <v>73</v>
@@ -71353,7 +71353,7 @@
         <v>74</v>
       </c>
       <c r="G655" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H655" t="s" s="2">
         <v>73</v>
@@ -71457,7 +71457,7 @@
         <v>74</v>
       </c>
       <c r="G656" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H656" t="s" s="2">
         <v>73</v>
